--- a/data/trans_orig/P36B01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B01-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de café o té en 2016</t>
+          <t>Población según la frecuencia de consumo de café o té en 2016 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88960</t>
+          <t>88697</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>126351</t>
+          <t>129384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80079</t>
+          <t>81225</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117367</t>
+          <t>116517</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>180729</t>
+          <t>180311</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>234769</t>
+          <t>233940</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11662</t>
+          <t>11722</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29298</t>
+          <t>28884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>10386</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14666</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34658</t>
+          <t>33841</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28397</t>
+          <t>27520</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19438</t>
+          <t>18673</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>20432</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42437</t>
+          <t>41702</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23224</t>
+          <t>22713</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22356</t>
+          <t>22621</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39051</t>
+          <t>39867</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>492901</t>
+          <t>491913</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>536945</t>
+          <t>537495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>520782</t>
+          <t>519944</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561039</t>
+          <t>560658</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1023940</t>
+          <t>1026340</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1087245</t>
+          <t>1087038</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,92%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152858</t>
+          <t>153315</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203662</t>
+          <t>201687</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131003</t>
+          <t>129544</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>177253</t>
+          <t>176910</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>294125</t>
+          <t>294056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>362134</t>
+          <t>360953</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15472</t>
+          <t>16741</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>35812</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18069</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38020</t>
+          <t>38048</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39039</t>
+          <t>38473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67185</t>
+          <t>67355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>14886</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35894</t>
+          <t>36100</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28458</t>
+          <t>26819</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29710</t>
+          <t>30030</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56452</t>
+          <t>57107</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20749</t>
+          <t>19952</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43714</t>
+          <t>43389</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>12573</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31091</t>
+          <t>32302</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38139</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68152</t>
+          <t>68975</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>735167</t>
+          <t>736949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>793461</t>
+          <t>791943</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>797381</t>
+          <t>798745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>850151</t>
+          <t>850408</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1553373</t>
+          <t>1554949</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1631207</t>
+          <t>1633639</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,14%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65723</t>
+          <t>63764</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102189</t>
+          <t>99481</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73344</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111742</t>
+          <t>107561</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149263</t>
+          <t>146729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>199158</t>
+          <t>198898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17765</t>
+          <t>18646</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>9563</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>23023</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19395</t>
+          <t>19584</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18219</t>
+          <t>19624</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13330</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32365</t>
+          <t>31640</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>628233</t>
+          <t>630042</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>668230</t>
+          <t>668826</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>650920</t>
+          <t>654427</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>692117</t>
+          <t>692632</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1294430</t>
+          <t>1294341</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1347891</t>
+          <t>1351369</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,81%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87953</t>
+          <t>90435</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128826</t>
+          <t>128266</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>96466</t>
+          <t>95950</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>140017</t>
+          <t>137810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>196785</t>
+          <t>196663</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>250459</t>
+          <t>254958</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26158</t>
+          <t>26242</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21341</t>
+          <t>20801</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,47 +2939,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>29162</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>19525</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>40615</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>2,05%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>29162</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>19447</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>40931</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11947</t>
+          <t>12272</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29081</t>
+          <t>29470</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32224</t>
+          <t>32608</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29018</t>
+          <t>30833</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>55199</t>
+          <t>54186</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>18451</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>39127</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18593</t>
+          <t>19515</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41003</t>
+          <t>40624</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>42645</t>
+          <t>40332</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70621</t>
+          <t>69728</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>741199</t>
+          <t>742032</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>787962</t>
+          <t>787967</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>836392</t>
+          <t>835907</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>884751</t>
+          <t>885841</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1593656</t>
+          <t>1588504</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1661482</t>
+          <t>1662477</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,08%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>436947</t>
+          <t>436231</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>516099</t>
+          <t>520007</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,47 +3473,47 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>12,87%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>15,34%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>438</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>455464</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>417344</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>499845</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
           <t>12,89%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>15,22%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>455464</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>413553</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>497229</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>878328</t>
+          <t>878727</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>988830</t>
+          <t>988479</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50200</t>
+          <t>50948</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>83656</t>
+          <t>83617</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34929</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>62522</t>
+          <t>63745</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>94409</t>
+          <t>95601</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>134890</t>
+          <t>136455</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>55175</t>
+          <t>54547</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>89442</t>
+          <t>88277</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>41077</t>
+          <t>40461</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>69983</t>
+          <t>68907</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>103746</t>
+          <t>103528</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>148144</t>
+          <t>152741</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>63709</t>
+          <t>66102</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>101943</t>
+          <t>103138</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>57210</t>
+          <t>54304</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>92000</t>
+          <t>89760</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>130312</t>
+          <t>128730</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>182036</t>
+          <t>177579</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2648102</t>
+          <t>2649657</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2743943</t>
+          <t>2743991</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2854982</t>
+          <t>2855265</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2949996</t>
+          <t>2949108</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5538480</t>
+          <t>5528900</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5667884</t>
+          <t>5665908</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B01-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88697</t>
+          <t>88326</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129384</t>
+          <t>129442</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81225</t>
+          <t>80659</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116517</t>
+          <t>117103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>180311</t>
+          <t>180482</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>233940</t>
+          <t>233372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28884</t>
+          <t>28052</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,82 +858,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4640</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10373</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>23387</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>15265</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>34658</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>1,74%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4640</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1810</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>10386</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>23387</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>14898</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>33841</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>29181</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18673</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20432</t>
+          <t>20251</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41702</t>
+          <t>41966</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22713</t>
+          <t>23059</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>22445</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18322</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39867</t>
+          <t>38793</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491913</t>
+          <t>493624</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>537495</t>
+          <t>537688</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>519944</t>
+          <t>521064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>560658</t>
+          <t>562661</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1026340</t>
+          <t>1028818</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1087038</t>
+          <t>1088256</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,01%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153315</t>
+          <t>153146</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>201687</t>
+          <t>202112</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129544</t>
+          <t>129293</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>176910</t>
+          <t>176783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>294056</t>
+          <t>293992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>360953</t>
+          <t>363077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16741</t>
+          <t>16098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35812</t>
+          <t>36157</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>18726</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38048</t>
+          <t>39768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38473</t>
+          <t>39024</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67355</t>
+          <t>67435</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>15412</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36100</t>
+          <t>37029</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26819</t>
+          <t>27323</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30030</t>
+          <t>29598</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57107</t>
+          <t>55502</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43389</t>
+          <t>43400</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12573</t>
+          <t>12621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32302</t>
+          <t>31772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38976</t>
+          <t>38465</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68975</t>
+          <t>68491</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>736949</t>
+          <t>735328</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>791943</t>
+          <t>792378</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>798745</t>
+          <t>796351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>850408</t>
+          <t>851458</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1554949</t>
+          <t>1549920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1633639</t>
+          <t>1627917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,86%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63764</t>
+          <t>68008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99481</t>
+          <t>102761</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>72350</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107561</t>
+          <t>107751</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>146729</t>
+          <t>149315</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>198898</t>
+          <t>199392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>15885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18646</t>
+          <t>19061</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23023</t>
+          <t>23365</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19584</t>
+          <t>20350</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19624</t>
+          <t>17946</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>13251</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31640</t>
+          <t>31828</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>630042</t>
+          <t>625252</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>668826</t>
+          <t>664930</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>654427</t>
+          <t>654554</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>692632</t>
+          <t>694138</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1294341</t>
+          <t>1290819</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1351369</t>
+          <t>1349042</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,66%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90435</t>
+          <t>89089</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128266</t>
+          <t>129152</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>95950</t>
+          <t>97473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>137810</t>
+          <t>142456</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>196663</t>
+          <t>194506</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>254958</t>
+          <t>251959</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>10190</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26242</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20801</t>
+          <t>21260</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19525</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>40615</t>
+          <t>41300</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12272</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29470</t>
+          <t>29790</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>14206</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32608</t>
+          <t>32034</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30833</t>
+          <t>29555</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54186</t>
+          <t>54533</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18451</t>
+          <t>17411</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39127</t>
+          <t>37417</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19515</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>40624</t>
+          <t>40813</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40332</t>
+          <t>40299</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69728</t>
+          <t>69231</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>742032</t>
+          <t>743032</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>787967</t>
+          <t>791810</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>835907</t>
+          <t>834021</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>885841</t>
+          <t>884056</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1588504</t>
+          <t>1591682</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1662477</t>
+          <t>1659821</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,95%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>436231</t>
+          <t>434989</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>520007</t>
+          <t>517337</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>417344</t>
+          <t>416658</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>499845</t>
+          <t>496841</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>878727</t>
+          <t>877144</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>988479</t>
+          <t>987209</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>50948</t>
+          <t>49958</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>83617</t>
+          <t>83041</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>36113</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>63745</t>
+          <t>64020</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>95601</t>
+          <t>94413</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>136455</t>
+          <t>138050</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>54547</t>
+          <t>55028</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>88277</t>
+          <t>88562</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>40461</t>
+          <t>40626</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>68907</t>
+          <t>69748</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>103528</t>
+          <t>103727</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>152741</t>
+          <t>149661</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>66102</t>
+          <t>66774</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>103138</t>
+          <t>104304</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>54304</t>
+          <t>55699</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>89760</t>
+          <t>90525</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>128730</t>
+          <t>131257</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>177579</t>
+          <t>181261</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2649657</t>
+          <t>2652089</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2743991</t>
+          <t>2747420</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2855265</t>
+          <t>2851640</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2949108</t>
+          <t>2951726</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5528900</t>
+          <t>5538958</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5665908</t>
+          <t>5670506</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
